--- a/artfynd/A 63736-2023 artfynd.xlsx
+++ b/artfynd/A 63736-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63736-2023 artfynd.xlsx
+++ b/artfynd/A 63736-2023 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>114462673</v>
       </c>
       <c r="B3" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 63736-2023 artfynd.xlsx
+++ b/artfynd/A 63736-2023 artfynd.xlsx
@@ -831,11 +831,6 @@
       <c r="E3" t="n">
         <v>205998</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>

--- a/artfynd/A 63736-2023 artfynd.xlsx
+++ b/artfynd/A 63736-2023 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>114462673</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,6 +830,11 @@
       </c>
       <c r="E3" t="n">
         <v>205998</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 63736-2023 artfynd.xlsx
+++ b/artfynd/A 63736-2023 artfynd.xlsx
@@ -816,7 +816,7 @@
         <v>114462673</v>
       </c>
       <c r="B3" t="n">
-        <v>56275</v>
+        <v>56276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
